--- a/testdata/registerDetails.xlsx
+++ b/testdata/registerDetails.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\playwrightautomation\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5AA5B98-2583-4F9F-BC80-6C1BA81129F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C631700-FD97-49C3-8C27-6DDF8C51463B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2736" yWindow="3864" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2736" yWindow="3720" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
